--- a/data/trans_dic/IP12B$diarrea-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$diarrea-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por diarrea o problemas intestinales</t>
+          <t>Menores que han limitado su actividad por síntomas o dolor por diarrea o problemas intestinales (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,96</t>
+          <t>0,0; 54,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,33; 53,89</t>
+          <t>7,55; 56,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,38</t>
+          <t>0,0; 39,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 84,93</t>
+          <t>0,0; 85,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,72</t>
+          <t>0,0; 26,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,21; 34,2</t>
+          <t>4,25; 37,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,53; 44,26</t>
+          <t>5,36; 44,69</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,65</t>
+          <t>0,0; 39,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 70,88</t>
+          <t>0,0; 71,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,34</t>
+          <t>0,0; 57,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,73</t>
+          <t>0,0; 56,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,4</t>
+          <t>0,0; 38,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,96; 39,01</t>
+          <t>4,79; 38,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,59</t>
+          <t>0,0; 16,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,07; 37,82</t>
+          <t>4,06; 33,56</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,8</t>
+          <t>0,0; 52,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,01</t>
+          <t>0,0; 39,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,06</t>
+          <t>0,0; 49,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,23</t>
+          <t>0,0; 33,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,48</t>
+          <t>0,0; 34,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,44</t>
+          <t>0,0; 25,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,92</t>
+          <t>0,0; 27,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,85</t>
+          <t>0,0; 25,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,15</t>
+          <t>0,0; 12,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,45</t>
+          <t>0,0; 29,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,97</t>
+          <t>0,0; 25,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 7,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,19</t>
+          <t>0,0; 13,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,12; 18,88</t>
+          <t>1,72; 18,42</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,48</t>
+          <t>0,0; 8,44</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,17</t>
+          <t>0,0; 39,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,82</t>
+          <t>0,0; 29,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,94</t>
+          <t>0,0; 44,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,59</t>
+          <t>0,0; 19,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,85</t>
+          <t>0,0; 22,4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,23</t>
+          <t>0,0; 14,51</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,96</t>
+          <t>0,0; 67,16</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8,88; 65,02</t>
+          <t>9,29; 67,42</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,05</t>
+          <t>0,0; 49,03</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,17; 46,25</t>
+          <t>6,34; 49,07</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,8; 16,17</t>
+          <t>2,81; 15,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,32; 14,27</t>
+          <t>3,18; 14,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,54; 14,05</t>
+          <t>2,61; 14,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,8; 15,5</t>
+          <t>2,82; 15,83</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,69; 20,3</t>
+          <t>5,4; 19,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,44; 11,25</t>
+          <t>1,44; 12,95</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,11; 13,72</t>
+          <t>4,01; 12,72</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,22; 13,9</t>
+          <t>5,02; 14,6</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,94; 10,58</t>
+          <t>2,95; 10,54</t>
         </is>
       </c>
     </row>
@@ -1404,4 +1405,1283 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por síntomas o dolor por diarrea o problemas intestinales (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1158</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2169</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1326</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1158</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2169</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>2826</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3109</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>652; 4877</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3772</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3404</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3859</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>649; 5700</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>729; 6074</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1153</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1411</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1816</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2581</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3144</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3507</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3180</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3324</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>603; 4869</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2959</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>534; 4417</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1187</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1274</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2283</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2985</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3379</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2630</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3893</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3969</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1312</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1860</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1263</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>3171</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3750</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4511</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2625</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4458</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5653</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3824</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>688; 7361</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3159</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>527</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>583</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1540</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>527</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1540</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>583</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3219</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3040</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4286</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2719</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4861</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2569</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2559</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>595; 4314</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3226</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>590; 4566</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>3430</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>4108</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>3679</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>3370</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>6684</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>2163</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>6800</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>10792</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>5842</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>1166; 6466</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>1928; 8584</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>1379; 7393</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>1315; 7394</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>3164; 11535</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>663; 5948</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>3532; 11221</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>5990; 17420</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>2915; 10404</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$diarrea-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$diarrea-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por diarrea o problemas intestinales (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por diarrea o problemas intestinales (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,17 +678,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,06</t>
+          <t>0,0; 53,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,55; 56,47</t>
+          <t>7,35; 59,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,25</t>
+          <t>0,0; 45,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,79</t>
+          <t>0,0; 24,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,25; 37,38</t>
+          <t>4,24; 37,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,36; 44,69</t>
+          <t>8,41; 44,17</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,46</t>
+          <t>0,0; 39,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -798,37 +798,37 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,09</t>
+          <t>0,0; 71,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,88</t>
+          <t>0,0; 68,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,94</t>
+          <t>0,0; 47,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,03</t>
+          <t>0,0; 30,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,79; 38,65</t>
+          <t>4,88; 37,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,69</t>
+          <t>0,0; 18,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,06; 33,56</t>
+          <t>3,95; 34,46</t>
         </is>
       </c>
     </row>
@@ -898,12 +898,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,34</t>
+          <t>0,0; 52,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,54</t>
+          <t>0,0; 38,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,2</t>
+          <t>0,0; 39,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,56</t>
+          <t>0,0; 33,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,67</t>
+          <t>0,0; 32,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,79</t>
+          <t>0,0; 25,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1008,27 +1008,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,12</t>
+          <t>0,0; 19,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,98</t>
+          <t>0,0; 22,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,77</t>
+          <t>0,0; 15,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,13</t>
+          <t>0,0; 21,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,02</t>
+          <t>0,0; 26,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1038,17 +1038,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,13</t>
+          <t>0,0; 15,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,72; 18,42</t>
+          <t>2,12; 18,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,44</t>
+          <t>0,0; 9,7</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,13</t>
+          <t>0,0; 29,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,6</t>
+          <t>0,0; 29,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,63</t>
+          <t>0,0; 45,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1148,17 +1148,17 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,1</t>
+          <t>0,0; 19,99</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,4</t>
+          <t>0,0; 22,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,51</t>
+          <t>0,0; 16,85</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,16</t>
+          <t>0,0; 68,07</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,29; 67,42</t>
+          <t>9,09; 66,75</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,03</t>
+          <t>0,0; 39,81</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,34; 49,07</t>
+          <t>6,31; 50,38</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,81; 15,59</t>
+          <t>2,8; 16,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,18; 14,15</t>
+          <t>2,26; 13,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,61; 14,0</t>
+          <t>3,31; 14,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,82; 15,83</t>
+          <t>2,83; 14,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,4; 19,67</t>
+          <t>5,6; 20,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,44; 12,95</t>
+          <t>1,46; 14,15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,01; 12,72</t>
+          <t>4,0; 13,38</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,02; 14,6</t>
+          <t>5,46; 14,44</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,95; 10,54</t>
+          <t>2,76; 10,66</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por diarrea o problemas intestinales (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por diarrea o problemas intestinales (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1639,17 +1639,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3109</t>
+          <t>0; 3086</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>652; 4877</t>
+          <t>635; 5139</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3772</t>
+          <t>0; 4373</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1669,17 +1669,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3859</t>
+          <t>0; 3562</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>649; 5700</t>
+          <t>647; 5760</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>729; 6074</t>
+          <t>1143; 6003</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2581</t>
+          <t>0; 2583</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1812,37 +1812,37 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3144</t>
+          <t>0; 3143</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3507</t>
+          <t>0; 4121</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3180</t>
+          <t>0; 2637</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3324</t>
+          <t>0; 2703</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>603; 4869</t>
+          <t>615; 4777</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 2959</t>
+          <t>0; 3246</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>534; 4417</t>
+          <t>520; 4536</t>
         </is>
       </c>
     </row>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2283</t>
+          <t>0; 2286</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2985</t>
+          <t>0; 2914</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3379</t>
+          <t>0; 2740</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2630</t>
+          <t>0; 2654</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3893</t>
+          <t>0; 3673</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3969</t>
+          <t>0; 3894</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2128,27 +2128,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3750</t>
+          <t>0; 2714</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4511</t>
+          <t>0; 3991</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2625</t>
+          <t>0; 3184</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4458</t>
+          <t>0; 3298</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5653</t>
+          <t>0; 6010</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2158,17 +2158,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3824</t>
+          <t>0; 4375</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>688; 7361</t>
+          <t>845; 7269</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 3159</t>
+          <t>0; 3632</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3219</t>
+          <t>0; 2451</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3040</t>
+          <t>0; 3023</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4286</t>
+          <t>0; 4377</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2321,17 +2321,17 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 2719</t>
+          <t>0; 2846</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 4861</t>
+          <t>0; 4791</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 2569</t>
+          <t>0; 2983</t>
         </is>
       </c>
     </row>
@@ -2469,12 +2469,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 2559</t>
+          <t>0; 2594</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>595; 4314</t>
+          <t>582; 4271</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 3226</t>
+          <t>0; 2619</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>590; 4566</t>
+          <t>587; 4688</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1166; 6466</t>
+          <t>1163; 6979</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1928; 8584</t>
+          <t>1374; 8455</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1379; 7393</t>
+          <t>1746; 7614</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1315; 7394</t>
+          <t>1320; 6767</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3164; 11535</t>
+          <t>3285; 11917</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>663; 5948</t>
+          <t>670; 6500</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3532; 11221</t>
+          <t>3529; 11799</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>5990; 17420</t>
+          <t>6516; 17225</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2915; 10404</t>
+          <t>2722; 10526</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$diarrea-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$diarrea-Clase-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>37,68%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>20,13%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>25,11%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>13,8%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>37,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,65</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,35; 59,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,5</t>
+          <t>0,0; 84,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 53,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,33; 53,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 85,53</t>
+          <t>0,0; 43,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,73</t>
+          <t>0,0; 24,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,24; 37,77</t>
+          <t>4,21; 34,2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,41; 44,17</t>
+          <t>5,53; 44,26</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>23,29%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>11,48%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7,58%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>9,37%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>26,08%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>23,29%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>11,48%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>7,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,51</t>
+          <t>0,0; 58,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 47,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,07</t>
+          <t>0,0; 38,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,01</t>
+          <t>0,0; 39,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,93</t>
+          <t>0,0; 70,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,88; 37,92</t>
+          <t>4,96; 39,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,31</t>
+          <t>0,0; 18,59</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,95; 34,46</t>
+          <t>4,07; 37,82</t>
         </is>
       </c>
     </row>
@@ -845,27 +845,27 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>9,71%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8,25%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>11,92%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>8,31%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9,71%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8,25%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -898,12 +898,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,4</t>
+          <t>0,0; 49,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,6</t>
+          <t>0,0; 34,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,89</t>
+          <t>0,0; 65,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,85</t>
+          <t>0,0; 36,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,71</t>
+          <t>0,0; 34,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,3</t>
+          <t>0,0; 25,44</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4,25%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8,23%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>4,43%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>7,55%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>3,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,25%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8,23%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,63</t>
+          <t>0,0; 17,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,99</t>
+          <t>0,0; 24,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,55</t>
+          <t>0,0; 18,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,59</t>
+          <t>0,0; 26,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 13,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,02</t>
+          <t>0,0; 15,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,12; 18,19</t>
+          <t>2,12; 18,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,7</t>
+          <t>0,0; 8,48</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>16,03%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>6,4%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>5,67%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>16,03%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 42,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 29,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,58</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 26,82</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,99</t>
+          <t>0,0; 21,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,08</t>
+          <t>0,0; 23,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,85</t>
+          <t>0,0; 17,23</t>
         </is>
       </c>
     </row>
@@ -1175,27 +1175,27 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>16,85%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>31,21%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>16,85%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>31,21%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 66,96</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,88; 65,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1243,12 +1243,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,09; 66,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,81</t>
+          <t>0,0; 40,05</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,31; 50,38</t>
+          <t>6,17; 46,25</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>7,22%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>11,4%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4,71%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>8,27%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>6,77%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>6,97%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>7,22%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>11,4%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,8; 16,83</t>
+          <t>2,8; 15,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,26; 13,93</t>
+          <t>5,69; 20,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,31; 14,42</t>
+          <t>1,44; 11,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,83; 14,49</t>
+          <t>2,8; 16,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,6; 20,32</t>
+          <t>2,32; 14,27</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,46; 14,15</t>
+          <t>2,54; 14,05</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,0; 13,38</t>
+          <t>4,11; 13,72</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,46; 14,44</t>
+          <t>5,22; 13,9</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,76; 10,66</t>
+          <t>2,94; 10,58</t>
         </is>
       </c>
     </row>
@@ -1438,14 +1438,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1533,27 +1533,27 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -1586,32 +1586,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>1158</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>2169</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>1326</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1500</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3086</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635; 5139</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4373</t>
+          <t>0; 3380</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3104</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>633; 4654</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3404</t>
+          <t>0; 4169</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3562</t>
+          <t>0; 3561</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>647; 5760</t>
+          <t>643; 5215</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1143; 6003</t>
+          <t>752; 6015</t>
         </is>
       </c>
     </row>
@@ -1696,32 +1696,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1749,32 +1749,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1411</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>613</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1153</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1411</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>641</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>663</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2583</t>
+          <t>0; 3535</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2666</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3143</t>
+          <t>0; 3356</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4121</t>
+          <t>0; 2593</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 2637</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2703</t>
+          <t>0; 3134</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>615; 4777</t>
+          <t>625; 4915</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3246</t>
+          <t>0; 3295</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>520; 4536</t>
+          <t>535; 4977</t>
         </is>
       </c>
     </row>
@@ -1912,27 +1912,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>520</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>627</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2286</t>
+          <t>0; 3369</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2914</t>
+          <t>0; 2683</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 2740</t>
+          <t>0; 2870</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2654</t>
+          <t>0; 2719</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3673</t>
+          <t>0; 3873</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3894</t>
+          <t>0; 3915</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2032,22 +2032,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2075,32 +2075,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1860</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>613</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>1312</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>617</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1860</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2714</t>
+          <t>0; 2671</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3991</t>
+          <t>0; 5643</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3184</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3298</t>
+          <t>0; 2616</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 6010</t>
+          <t>0; 4661</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2703</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4375</t>
+          <t>0; 4425</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>845; 7269</t>
+          <t>847; 7545</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 3632</t>
+          <t>0; 3173</t>
         </is>
       </c>
     </row>
@@ -2185,32 +2185,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2238,32 +2238,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1540</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>527</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>583</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1540</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 2451</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4124</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3023</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2400</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4377</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2755</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 2846</t>
+          <t>0; 3074</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 4791</t>
+          <t>0; 5174</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 2983</t>
+          <t>0; 3051</t>
         </is>
       </c>
     </row>
@@ -2348,12 +2348,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2363,12 +2363,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2401,12 +2401,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>642</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2416,12 +2416,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2551</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>568; 4161</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 2594</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>582; 4271</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 2619</t>
+          <t>0; 2635</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>587; 4688</t>
+          <t>574; 4303</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2511,32 +2511,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2564,32 +2564,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>3370</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>6684</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2163</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>3430</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>4108</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>3679</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>3370</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>6684</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>2163</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1163; 6979</t>
+          <t>1308; 7239</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1374; 8455</t>
+          <t>3336; 11902</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1746; 7614</t>
+          <t>659; 5171</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1320; 6767</t>
+          <t>1163; 6705</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3285; 11917</t>
+          <t>1407; 8659</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>670; 6500</t>
+          <t>1343; 7417</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3529; 11799</t>
+          <t>3625; 12097</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>6516; 17225</t>
+          <t>6223; 16581</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2722; 10526</t>
+          <t>2898; 10445</t>
         </is>
       </c>
     </row>
